--- a/references/Natalus_NanoZ_ProbeCard_Wiring.xlsx
+++ b/references/Natalus_NanoZ_ProbeCard_Wiring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\automationproject\labviewtest\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E426D300-4B04-40EB-873A-FED4F08F0315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763B82AA-26F0-401A-9155-EEEDF3EF6A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="432">
   <si>
     <t>Device</t>
   </si>
@@ -64,624 +64,1077 @@
     <t>NanoZ Chip</t>
   </si>
   <si>
+    <t>S 1</t>
+  </si>
+  <si>
+    <t>J1-11</t>
+  </si>
+  <si>
+    <t>Device header 01</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>DAQ 01</t>
+  </si>
+  <si>
+    <t>Chip 1</t>
+  </si>
+  <si>
+    <t>H 1</t>
+  </si>
+  <si>
+    <t>J1-12</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>S 2</t>
+  </si>
+  <si>
+    <t>J1-13</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>S 3</t>
+  </si>
+  <si>
+    <t>J1-14</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>H 2</t>
+  </si>
+  <si>
+    <t>J1-28</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>S 4</t>
+  </si>
+  <si>
+    <t>J1-29</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>J1-30</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>J1-15</t>
+  </si>
+  <si>
+    <t>Device header 02</t>
+  </si>
+  <si>
+    <t>Chip 2</t>
+  </si>
+  <si>
+    <t>J1-16</t>
+  </si>
+  <si>
+    <t>J1-17</t>
+  </si>
+  <si>
+    <t>J1-18</t>
+  </si>
+  <si>
+    <t>J2-49</t>
+  </si>
+  <si>
+    <t>J1-26</t>
+  </si>
+  <si>
+    <t>J1-27</t>
+  </si>
+  <si>
+    <t>J1-19</t>
+  </si>
+  <si>
+    <t>Device header 03</t>
+  </si>
+  <si>
+    <t>DAQ 02</t>
+  </si>
+  <si>
+    <t>J1-20</t>
+  </si>
+  <si>
+    <t>J1-21</t>
+  </si>
+  <si>
+    <t>J1-22</t>
+  </si>
+  <si>
+    <t>J2-48</t>
+  </si>
+  <si>
+    <t>J2-47</t>
+  </si>
+  <si>
+    <t>J2-50</t>
+  </si>
+  <si>
+    <t>J1-23</t>
+  </si>
+  <si>
+    <t>Device header 04</t>
+  </si>
+  <si>
+    <t>J1-24</t>
+  </si>
+  <si>
+    <t>J1-25</t>
+  </si>
+  <si>
+    <t>J2-2</t>
+  </si>
+  <si>
+    <t>J2-43</t>
+  </si>
+  <si>
+    <t>J2-46</t>
+  </si>
+  <si>
+    <t>J2-45</t>
+  </si>
+  <si>
+    <t>J2-1</t>
+  </si>
+  <si>
+    <t>Device header 05</t>
+  </si>
+  <si>
+    <t>DAQ 03</t>
+  </si>
+  <si>
+    <t>J2-4</t>
+  </si>
+  <si>
+    <t>J2-3</t>
+  </si>
+  <si>
+    <t>J2-6</t>
+  </si>
+  <si>
+    <t>J2-42</t>
+  </si>
+  <si>
+    <t>J2-41</t>
+  </si>
+  <si>
+    <t>J2-44</t>
+  </si>
+  <si>
+    <t>J2-5</t>
+  </si>
+  <si>
+    <t>Device header 06</t>
+  </si>
+  <si>
+    <t>J2-8</t>
+  </si>
+  <si>
+    <t>J2-7</t>
+  </si>
+  <si>
+    <t>J2-10</t>
+  </si>
+  <si>
+    <t>J2-37</t>
+  </si>
+  <si>
+    <t>J2-40</t>
+  </si>
+  <si>
+    <t>J2-39</t>
+  </si>
+  <si>
+    <t>J2-9</t>
+  </si>
+  <si>
+    <t>Device header 07</t>
+  </si>
+  <si>
+    <t>DAQ 04</t>
+  </si>
+  <si>
+    <t>J2-12</t>
+  </si>
+  <si>
+    <t>J2-11</t>
+  </si>
+  <si>
+    <t>J2-14</t>
+  </si>
+  <si>
+    <t>J2-36</t>
+  </si>
+  <si>
+    <t>J2-35</t>
+  </si>
+  <si>
+    <t>J2-38</t>
+  </si>
+  <si>
+    <t>J2-13</t>
+  </si>
+  <si>
+    <t>Device header 08</t>
+  </si>
+  <si>
+    <t>J2-16</t>
+  </si>
+  <si>
+    <t>J2-15</t>
+  </si>
+  <si>
+    <t>J2-18</t>
+  </si>
+  <si>
+    <t>J2-31</t>
+  </si>
+  <si>
+    <t>J2-34</t>
+  </si>
+  <si>
+    <t>J2-33</t>
+  </si>
+  <si>
+    <t>J2-17</t>
+  </si>
+  <si>
+    <t>Device header 09</t>
+  </si>
+  <si>
+    <t>DAQ 05</t>
+  </si>
+  <si>
+    <t>J2-20</t>
+  </si>
+  <si>
+    <t>J2-19</t>
+  </si>
+  <si>
+    <t>J2-22</t>
+  </si>
+  <si>
+    <t>J2-30</t>
+  </si>
+  <si>
+    <t>J2-29</t>
+  </si>
+  <si>
+    <t>J2-32</t>
+  </si>
+  <si>
+    <t>J2-21</t>
+  </si>
+  <si>
+    <t>Device header 10</t>
+  </si>
+  <si>
+    <t>J2-24</t>
+  </si>
+  <si>
+    <t>J2-23</t>
+  </si>
+  <si>
+    <t>J2-26</t>
+  </si>
+  <si>
+    <t>J2-25</t>
+  </si>
+  <si>
+    <t>J2-28</t>
+  </si>
+  <si>
+    <t>J2-27</t>
+  </si>
+  <si>
+    <t>J3-1</t>
+  </si>
+  <si>
+    <t>Device header 11</t>
+  </si>
+  <si>
+    <t>DAQ 06</t>
+  </si>
+  <si>
+    <t>J3-2</t>
+  </si>
+  <si>
+    <t>J3-3</t>
+  </si>
+  <si>
+    <t>J3-4</t>
+  </si>
+  <si>
+    <t>J3-48</t>
+  </si>
+  <si>
+    <t>J3-49</t>
+  </si>
+  <si>
+    <t>J3-50</t>
+  </si>
+  <si>
+    <t>J3-5</t>
+  </si>
+  <si>
+    <t>Device header 12</t>
+  </si>
+  <si>
+    <t>J3-6</t>
+  </si>
+  <si>
+    <t>J3-7</t>
+  </si>
+  <si>
+    <t>J3-8</t>
+  </si>
+  <si>
+    <t>J3-45</t>
+  </si>
+  <si>
+    <t>J3-46</t>
+  </si>
+  <si>
+    <t>J3-47</t>
+  </si>
+  <si>
+    <t>J3-9</t>
+  </si>
+  <si>
+    <t>Device header 13</t>
+  </si>
+  <si>
+    <t>DAQ 07</t>
+  </si>
+  <si>
+    <t>J3-10</t>
+  </si>
+  <si>
+    <t>J3-11</t>
+  </si>
+  <si>
+    <t>J3-12</t>
+  </si>
+  <si>
+    <t>J3-42</t>
+  </si>
+  <si>
+    <t>J3-43</t>
+  </si>
+  <si>
+    <t>J3-44</t>
+  </si>
+  <si>
+    <t>J3-13</t>
+  </si>
+  <si>
+    <t>Device header 14</t>
+  </si>
+  <si>
+    <t>J3-14</t>
+  </si>
+  <si>
+    <t>J3-15</t>
+  </si>
+  <si>
+    <t>J3-16</t>
+  </si>
+  <si>
+    <t>J3-39</t>
+  </si>
+  <si>
+    <t>J3-40</t>
+  </si>
+  <si>
+    <t>J3-41</t>
+  </si>
+  <si>
+    <t>J3-17</t>
+  </si>
+  <si>
+    <t>Device header 15</t>
+  </si>
+  <si>
+    <t>DAQ 08</t>
+  </si>
+  <si>
+    <t>J3-18</t>
+  </si>
+  <si>
+    <t>J3-19</t>
+  </si>
+  <si>
+    <t>J3-20</t>
+  </si>
+  <si>
+    <t>J3-36</t>
+  </si>
+  <si>
+    <t>J3-37</t>
+  </si>
+  <si>
+    <t>J3-38</t>
+  </si>
+  <si>
+    <t>J3-21</t>
+  </si>
+  <si>
+    <t>Device header 16</t>
+  </si>
+  <si>
+    <t>J3-22</t>
+  </si>
+  <si>
+    <t>J3-23</t>
+  </si>
+  <si>
+    <t>J3-24</t>
+  </si>
+  <si>
+    <t>J3-33</t>
+  </si>
+  <si>
+    <t>J3-34</t>
+  </si>
+  <si>
+    <t>J3-35</t>
+  </si>
+  <si>
+    <t>J3-25</t>
+  </si>
+  <si>
+    <t>Device header 17</t>
+  </si>
+  <si>
+    <t>DAQ 09</t>
+  </si>
+  <si>
+    <t>J4-2</t>
+  </si>
+  <si>
+    <t>J4-1</t>
+  </si>
+  <si>
+    <t>J4-4</t>
+  </si>
+  <si>
+    <t>J3-30</t>
+  </si>
+  <si>
+    <t>J3-31</t>
+  </si>
+  <si>
+    <t>J3-32</t>
+  </si>
+  <si>
+    <t>J4-3</t>
+  </si>
+  <si>
+    <t>Device header 18</t>
+  </si>
+  <si>
+    <t>J4-6</t>
+  </si>
+  <si>
+    <t>J4-5</t>
+  </si>
+  <si>
+    <t>J4-8</t>
+  </si>
+  <si>
+    <t>J3-27</t>
+  </si>
+  <si>
+    <t>J3-28</t>
+  </si>
+  <si>
+    <t>J3-29</t>
+  </si>
+  <si>
+    <t>J4-7</t>
+  </si>
+  <si>
+    <t>Device header 19</t>
+  </si>
+  <si>
+    <t>DAQ 10</t>
+  </si>
+  <si>
+    <t>J4-10</t>
+  </si>
+  <si>
+    <t>J4-9</t>
+  </si>
+  <si>
+    <t>J4-12</t>
+  </si>
+  <si>
+    <t>J4-50</t>
+  </si>
+  <si>
+    <t>J4-49</t>
+  </si>
+  <si>
+    <t>J3-26</t>
+  </si>
+  <si>
+    <t>J4-11</t>
+  </si>
+  <si>
+    <t>Device header 20</t>
+  </si>
+  <si>
+    <t>J4-14</t>
+  </si>
+  <si>
+    <t>J4-13</t>
+  </si>
+  <si>
+    <t>J4-16</t>
+  </si>
+  <si>
+    <t>J4-45</t>
+  </si>
+  <si>
+    <t>J4-48</t>
+  </si>
+  <si>
+    <t>J4-47</t>
+  </si>
+  <si>
+    <t>NanoZ package pin 6 is not connected on any device - leave floating.</t>
+  </si>
+  <si>
+    <t>Source: Natalus_NanoZ_ProbeCard_Wiring_Manual.pdf Appendix B ("engineering draft - verify against hardware before production release").</t>
+  </si>
+  <si>
+    <t>J1 Connector - Physical 2x25 Layout</t>
+  </si>
+  <si>
+    <t>Top row - pin #</t>
+  </si>
+  <si>
+    <t>Top row - signal</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>1 GND</t>
+  </si>
+  <si>
+    <t>1 H 2</t>
+  </si>
+  <si>
+    <t>2 S 4</t>
+  </si>
+  <si>
+    <t>4 H 1</t>
+  </si>
+  <si>
+    <t>3 S 3</t>
+  </si>
+  <si>
+    <t>3 H 1</t>
+  </si>
+  <si>
+    <t>2 S 3</t>
+  </si>
+  <si>
+    <t>2 H 1</t>
+  </si>
+  <si>
+    <t>1 S 3</t>
+  </si>
+  <si>
+    <t>1 H 1</t>
+  </si>
+  <si>
+    <t>Bottom row - pin #</t>
+  </si>
+  <si>
+    <t>Bottom row - signal</t>
+  </si>
+  <si>
+    <t>1 S 4</t>
+  </si>
+  <si>
+    <t>2 GND</t>
+  </si>
+  <si>
+    <t>4 S 2</t>
+  </si>
+  <si>
+    <t>4 S 1</t>
+  </si>
+  <si>
+    <t>3 S 2</t>
+  </si>
+  <si>
+    <t>3 S 1</t>
+  </si>
+  <si>
+    <t>2 S 2</t>
+  </si>
+  <si>
+    <t>2 S 1</t>
+  </si>
+  <si>
+    <t>1 S 2</t>
+  </si>
+  <si>
+    <t>1 S 1</t>
+  </si>
+  <si>
+    <t>J2 Connector - Physical 2x25 Layout</t>
+  </si>
+  <si>
+    <t>3 GND</t>
+  </si>
+  <si>
+    <t>3 H 2</t>
+  </si>
+  <si>
+    <t>4 S 4</t>
+  </si>
+  <si>
+    <t>5 GND</t>
+  </si>
+  <si>
+    <t>5 H 2</t>
+  </si>
+  <si>
+    <t>6 S 4</t>
+  </si>
+  <si>
+    <t>7 GND</t>
+  </si>
+  <si>
+    <t>7 H 2</t>
+  </si>
+  <si>
+    <t>8 S 4</t>
+  </si>
+  <si>
+    <t>9 GND</t>
+  </si>
+  <si>
+    <t>9 H 2</t>
+  </si>
+  <si>
+    <t>10 S 4</t>
+  </si>
+  <si>
+    <t>10 S 3</t>
+  </si>
+  <si>
+    <t>10 H 1</t>
+  </si>
+  <si>
+    <t>9 S 3</t>
+  </si>
+  <si>
+    <t>9 H 1</t>
+  </si>
+  <si>
+    <t>8 S 3</t>
+  </si>
+  <si>
+    <t>8 H 1</t>
+  </si>
+  <si>
+    <t>7 S 3</t>
+  </si>
+  <si>
+    <t>7 H 1</t>
+  </si>
+  <si>
+    <t>6 S 3</t>
+  </si>
+  <si>
+    <t>6 H 1</t>
+  </si>
+  <si>
+    <t>5 S 3</t>
+  </si>
+  <si>
+    <t>5 H 1</t>
+  </si>
+  <si>
+    <t>4 S 3</t>
+  </si>
+  <si>
+    <t>2 H 2</t>
+  </si>
+  <si>
+    <t>3 S 4</t>
+  </si>
+  <si>
+    <t>4 GND</t>
+  </si>
+  <si>
+    <t>4 H 2</t>
+  </si>
+  <si>
+    <t>5 S 4</t>
+  </si>
+  <si>
+    <t>6 GND</t>
+  </si>
+  <si>
+    <t>6 H 2</t>
+  </si>
+  <si>
+    <t>7 S 4</t>
+  </si>
+  <si>
+    <t>8 GND</t>
+  </si>
+  <si>
+    <t>8 H 2</t>
+  </si>
+  <si>
+    <t>9 S 4</t>
+  </si>
+  <si>
+    <t>10 GND</t>
+  </si>
+  <si>
+    <t>10 H 2</t>
+  </si>
+  <si>
+    <t>10 S 2</t>
+  </si>
+  <si>
+    <t>10 S 1</t>
+  </si>
+  <si>
+    <t>9 S 2</t>
+  </si>
+  <si>
+    <t>9 S 1</t>
+  </si>
+  <si>
+    <t>8 S 2</t>
+  </si>
+  <si>
+    <t>8 S 1</t>
+  </si>
+  <si>
+    <t>7 S 2</t>
+  </si>
+  <si>
+    <t>7 S 1</t>
+  </si>
+  <si>
+    <t>6 S 2</t>
+  </si>
+  <si>
+    <t>6 S 1</t>
+  </si>
+  <si>
+    <t>5 S 2</t>
+  </si>
+  <si>
+    <t>5 S 1</t>
+  </si>
+  <si>
+    <t>J3 Connector - Physical 2x25 Layout</t>
+  </si>
+  <si>
+    <t>11 GND</t>
+  </si>
+  <si>
+    <t>11 H 2</t>
+  </si>
+  <si>
+    <t>12 S 4</t>
+  </si>
+  <si>
+    <t>13 GND</t>
+  </si>
+  <si>
+    <t>13 H 2</t>
+  </si>
+  <si>
+    <t>14 S 4</t>
+  </si>
+  <si>
+    <t>15 GND</t>
+  </si>
+  <si>
+    <t>15 H 2</t>
+  </si>
+  <si>
+    <t>16 S 4</t>
+  </si>
+  <si>
+    <t>17 GND</t>
+  </si>
+  <si>
+    <t>17 H 2</t>
+  </si>
+  <si>
+    <t>18 S 4</t>
+  </si>
+  <si>
+    <t>19 GND</t>
+  </si>
+  <si>
+    <t>16 S 3</t>
+  </si>
+  <si>
+    <t>16 H 1</t>
+  </si>
+  <si>
+    <t>15 S 3</t>
+  </si>
+  <si>
+    <t>15 H 1</t>
+  </si>
+  <si>
+    <t>14 S 3</t>
+  </si>
+  <si>
+    <t>14 H 1</t>
+  </si>
+  <si>
+    <t>13 S 3</t>
+  </si>
+  <si>
+    <t>13 H 1</t>
+  </si>
+  <si>
+    <t>12 S 3</t>
+  </si>
+  <si>
+    <t>12 H 1</t>
+  </si>
+  <si>
+    <t>11 S 3</t>
+  </si>
+  <si>
+    <t>11 H 1</t>
+  </si>
+  <si>
+    <t>11 S 4</t>
+  </si>
+  <si>
+    <t>12 GND</t>
+  </si>
+  <si>
+    <t>12 H 2</t>
+  </si>
+  <si>
+    <t>13 S 4</t>
+  </si>
+  <si>
+    <t>14 GND</t>
+  </si>
+  <si>
+    <t>14 H 2</t>
+  </si>
+  <si>
+    <t>15 S 4</t>
+  </si>
+  <si>
+    <t>16 GND</t>
+  </si>
+  <si>
+    <t>16 H 2</t>
+  </si>
+  <si>
+    <t>17 S 4</t>
+  </si>
+  <si>
+    <t>18 GND</t>
+  </si>
+  <si>
+    <t>18 H 2</t>
+  </si>
+  <si>
+    <t>17 S 1</t>
+  </si>
+  <si>
+    <t>16 S 2</t>
+  </si>
+  <si>
+    <t>16 S 1</t>
+  </si>
+  <si>
+    <t>15 S 2</t>
+  </si>
+  <si>
+    <t>15 S 1</t>
+  </si>
+  <si>
+    <t>14 S 2</t>
+  </si>
+  <si>
+    <t>14 S 1</t>
+  </si>
+  <si>
+    <t>13 S 2</t>
+  </si>
+  <si>
+    <t>13 S 1</t>
+  </si>
+  <si>
+    <t>12 S 2</t>
+  </si>
+  <si>
+    <t>12 S 1</t>
+  </si>
+  <si>
+    <t>11 S 2</t>
+  </si>
+  <si>
+    <t>11 S 1</t>
+  </si>
+  <si>
+    <t>J4 Connector - Physical 2x25 Layout</t>
+  </si>
+  <si>
+    <t>19 H 2</t>
+  </si>
+  <si>
+    <t>20 S 4</t>
+  </si>
+  <si>
+    <t>20 S 3</t>
+  </si>
+  <si>
+    <t>20 H 1</t>
+  </si>
+  <si>
+    <t>19 S 3</t>
+  </si>
+  <si>
+    <t>19 H 1</t>
+  </si>
+  <si>
+    <t>18 S 3</t>
+  </si>
+  <si>
+    <t>18 H 1</t>
+  </si>
+  <si>
+    <t>17 S 3</t>
+  </si>
+  <si>
+    <t>17 H 1</t>
+  </si>
+  <si>
+    <t>19 S 4</t>
+  </si>
+  <si>
+    <t>20 GND</t>
+  </si>
+  <si>
+    <t>20 H 2</t>
+  </si>
+  <si>
+    <t>20 S 2</t>
+  </si>
+  <si>
+    <t>20 S 1</t>
+  </si>
+  <si>
+    <t>19 S 2</t>
+  </si>
+  <si>
+    <t>19 S 1</t>
+  </si>
+  <si>
+    <t>18 S 2</t>
+  </si>
+  <si>
+    <t>18 S 1</t>
+  </si>
+  <si>
+    <t>17 S 2</t>
+  </si>
+  <si>
+    <t>JP20</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>gnd</t>
+  </si>
+  <si>
+    <t>nc</t>
+  </si>
+  <si>
+    <t>DAQ ports</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Die Pads</t>
+  </si>
+  <si>
+    <t>Pad</t>
+  </si>
+  <si>
+    <t>Breakout Pin</t>
+  </si>
+  <si>
     <t>Sensor 1</t>
   </si>
   <si>
-    <t>J1-11</t>
-  </si>
-  <si>
-    <t>Device header 01</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>DAQ 01</t>
-  </si>
-  <si>
-    <t>Chip 1</t>
-  </si>
-  <si>
     <t>Heater 1</t>
   </si>
   <si>
-    <t>J1-12</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
     <t>Sensor 2</t>
   </si>
   <si>
-    <t>J1-13</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
     <t>Sensor 3</t>
   </si>
   <si>
-    <t>J1-14</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
     <t>Heater 2</t>
   </si>
   <si>
-    <t>J1-28</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
     <t>Sensor 4</t>
   </si>
   <si>
-    <t>J1-29</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
     <t>Ground</t>
   </si>
   <si>
-    <t>J1-30</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>J1-15</t>
-  </si>
-  <si>
-    <t>Device header 02</t>
-  </si>
-  <si>
-    <t>Chip 2</t>
-  </si>
-  <si>
-    <t>J1-16</t>
-  </si>
-  <si>
-    <t>J1-17</t>
-  </si>
-  <si>
-    <t>J1-18</t>
-  </si>
-  <si>
-    <t>J2-49</t>
-  </si>
-  <si>
-    <t>J1-26</t>
-  </si>
-  <si>
-    <t>J1-27</t>
-  </si>
-  <si>
-    <t>J1-19</t>
-  </si>
-  <si>
-    <t>Device header 03</t>
-  </si>
-  <si>
-    <t>DAQ 02</t>
-  </si>
-  <si>
-    <t>J1-20</t>
-  </si>
-  <si>
-    <t>J1-21</t>
-  </si>
-  <si>
-    <t>J1-22</t>
-  </si>
-  <si>
-    <t>J2-48</t>
-  </si>
-  <si>
-    <t>J2-47</t>
-  </si>
-  <si>
-    <t>J2-50</t>
-  </si>
-  <si>
-    <t>J1-23</t>
-  </si>
-  <si>
-    <t>Device header 04</t>
-  </si>
-  <si>
-    <t>J1-24</t>
-  </si>
-  <si>
-    <t>J1-25</t>
-  </si>
-  <si>
-    <t>J2-2</t>
-  </si>
-  <si>
-    <t>J2-43</t>
-  </si>
-  <si>
-    <t>J2-46</t>
-  </si>
-  <si>
-    <t>J2-45</t>
-  </si>
-  <si>
-    <t>J2-1</t>
-  </si>
-  <si>
-    <t>Device header 05</t>
-  </si>
-  <si>
-    <t>DAQ 03</t>
-  </si>
-  <si>
-    <t>J2-4</t>
-  </si>
-  <si>
-    <t>J2-3</t>
-  </si>
-  <si>
-    <t>J2-6</t>
-  </si>
-  <si>
-    <t>J2-42</t>
-  </si>
-  <si>
-    <t>J2-41</t>
-  </si>
-  <si>
-    <t>J2-44</t>
-  </si>
-  <si>
-    <t>J2-5</t>
-  </si>
-  <si>
-    <t>Device header 06</t>
-  </si>
-  <si>
-    <t>J2-8</t>
-  </si>
-  <si>
-    <t>J2-7</t>
-  </si>
-  <si>
-    <t>J2-10</t>
-  </si>
-  <si>
-    <t>J2-37</t>
-  </si>
-  <si>
-    <t>J2-40</t>
-  </si>
-  <si>
-    <t>J2-39</t>
-  </si>
-  <si>
-    <t>J2-9</t>
-  </si>
-  <si>
-    <t>Device header 07</t>
-  </si>
-  <si>
-    <t>DAQ 04</t>
-  </si>
-  <si>
-    <t>J2-12</t>
-  </si>
-  <si>
-    <t>J2-11</t>
-  </si>
-  <si>
-    <t>J2-14</t>
-  </si>
-  <si>
-    <t>J2-36</t>
-  </si>
-  <si>
-    <t>J2-35</t>
-  </si>
-  <si>
-    <t>J2-38</t>
-  </si>
-  <si>
-    <t>J2-13</t>
-  </si>
-  <si>
-    <t>Device header 08</t>
-  </si>
-  <si>
-    <t>J2-16</t>
-  </si>
-  <si>
-    <t>J2-15</t>
-  </si>
-  <si>
-    <t>J2-18</t>
-  </si>
-  <si>
-    <t>J2-31</t>
-  </si>
-  <si>
-    <t>J2-34</t>
-  </si>
-  <si>
-    <t>J2-33</t>
-  </si>
-  <si>
-    <t>J2-17</t>
-  </si>
-  <si>
-    <t>Device header 09</t>
-  </si>
-  <si>
-    <t>DAQ 05</t>
-  </si>
-  <si>
-    <t>J2-20</t>
-  </si>
-  <si>
-    <t>J2-19</t>
-  </si>
-  <si>
-    <t>J2-22</t>
-  </si>
-  <si>
-    <t>J2-30</t>
-  </si>
-  <si>
-    <t>J2-29</t>
-  </si>
-  <si>
-    <t>J2-32</t>
-  </si>
-  <si>
-    <t>J2-21</t>
-  </si>
-  <si>
-    <t>Device header 10</t>
-  </si>
-  <si>
-    <t>J2-24</t>
-  </si>
-  <si>
-    <t>J2-23</t>
-  </si>
-  <si>
-    <t>J2-26</t>
-  </si>
-  <si>
-    <t>J2-25</t>
-  </si>
-  <si>
-    <t>J2-28</t>
-  </si>
-  <si>
-    <t>J2-27</t>
-  </si>
-  <si>
-    <t>J3-1</t>
-  </si>
-  <si>
-    <t>Device header 11</t>
-  </si>
-  <si>
-    <t>DAQ 06</t>
-  </si>
-  <si>
-    <t>J3-2</t>
-  </si>
-  <si>
-    <t>J3-3</t>
-  </si>
-  <si>
-    <t>J3-4</t>
-  </si>
-  <si>
-    <t>J3-48</t>
-  </si>
-  <si>
-    <t>J3-49</t>
-  </si>
-  <si>
-    <t>J3-50</t>
-  </si>
-  <si>
-    <t>J3-5</t>
-  </si>
-  <si>
-    <t>Device header 12</t>
-  </si>
-  <si>
-    <t>J3-6</t>
-  </si>
-  <si>
-    <t>J3-7</t>
-  </si>
-  <si>
-    <t>J3-8</t>
-  </si>
-  <si>
-    <t>J3-45</t>
-  </si>
-  <si>
-    <t>J3-46</t>
-  </si>
-  <si>
-    <t>J3-47</t>
-  </si>
-  <si>
-    <t>J3-9</t>
-  </si>
-  <si>
-    <t>Device header 13</t>
-  </si>
-  <si>
-    <t>DAQ 07</t>
-  </si>
-  <si>
-    <t>J3-10</t>
-  </si>
-  <si>
-    <t>J3-11</t>
-  </si>
-  <si>
-    <t>J3-12</t>
-  </si>
-  <si>
-    <t>J3-42</t>
-  </si>
-  <si>
-    <t>J3-43</t>
-  </si>
-  <si>
-    <t>J3-44</t>
-  </si>
-  <si>
-    <t>J3-13</t>
-  </si>
-  <si>
-    <t>Device header 14</t>
-  </si>
-  <si>
-    <t>J3-14</t>
-  </si>
-  <si>
-    <t>J3-15</t>
-  </si>
-  <si>
-    <t>J3-16</t>
-  </si>
-  <si>
-    <t>J3-39</t>
-  </si>
-  <si>
-    <t>J3-40</t>
-  </si>
-  <si>
-    <t>J3-41</t>
-  </si>
-  <si>
-    <t>J3-17</t>
-  </si>
-  <si>
-    <t>Device header 15</t>
-  </si>
-  <si>
-    <t>DAQ 08</t>
-  </si>
-  <si>
-    <t>J3-18</t>
-  </si>
-  <si>
-    <t>J3-19</t>
-  </si>
-  <si>
-    <t>J3-20</t>
-  </si>
-  <si>
-    <t>J3-36</t>
-  </si>
-  <si>
-    <t>J3-37</t>
-  </si>
-  <si>
-    <t>J3-38</t>
-  </si>
-  <si>
-    <t>J3-21</t>
-  </si>
-  <si>
-    <t>Device header 16</t>
-  </si>
-  <si>
-    <t>J3-22</t>
-  </si>
-  <si>
-    <t>J3-23</t>
-  </si>
-  <si>
-    <t>J3-24</t>
-  </si>
-  <si>
-    <t>J3-33</t>
-  </si>
-  <si>
-    <t>J3-34</t>
-  </si>
-  <si>
-    <t>J3-35</t>
-  </si>
-  <si>
-    <t>J3-25</t>
-  </si>
-  <si>
-    <t>Device header 17</t>
-  </si>
-  <si>
-    <t>DAQ 09</t>
-  </si>
-  <si>
-    <t>J4-2</t>
-  </si>
-  <si>
-    <t>J4-1</t>
-  </si>
-  <si>
-    <t>J4-4</t>
-  </si>
-  <si>
-    <t>J3-30</t>
-  </si>
-  <si>
-    <t>J3-31</t>
-  </si>
-  <si>
-    <t>J3-32</t>
-  </si>
-  <si>
-    <t>J4-3</t>
-  </si>
-  <si>
-    <t>Device header 18</t>
-  </si>
-  <si>
-    <t>J4-6</t>
-  </si>
-  <si>
-    <t>J4-5</t>
-  </si>
-  <si>
-    <t>J4-8</t>
-  </si>
-  <si>
-    <t>J3-27</t>
-  </si>
-  <si>
-    <t>J3-28</t>
-  </si>
-  <si>
-    <t>J3-29</t>
-  </si>
-  <si>
-    <t>J4-7</t>
-  </si>
-  <si>
-    <t>Device header 19</t>
-  </si>
-  <si>
-    <t>DAQ 10</t>
-  </si>
-  <si>
-    <t>J4-10</t>
-  </si>
-  <si>
-    <t>J4-9</t>
-  </si>
-  <si>
-    <t>J4-12</t>
-  </si>
-  <si>
-    <t>J4-50</t>
-  </si>
-  <si>
-    <t>J4-49</t>
-  </si>
-  <si>
-    <t>J3-26</t>
-  </si>
-  <si>
-    <t>J4-11</t>
-  </si>
-  <si>
-    <t>Device header 20</t>
-  </si>
-  <si>
-    <t>J4-14</t>
-  </si>
-  <si>
-    <t>J4-13</t>
-  </si>
-  <si>
-    <t>J4-16</t>
-  </si>
-  <si>
-    <t>J4-45</t>
-  </si>
-  <si>
-    <t>J4-48</t>
-  </si>
-  <si>
-    <t>J4-47</t>
-  </si>
-  <si>
-    <t>NanoZ package pin 6 is not connected on any device - leave floating.</t>
-  </si>
-  <si>
-    <t>Source: Natalus_NanoZ_ProbeCard_Wiring_Manual.pdf Appendix B ("engineering draft - verify against hardware before production release").</t>
-  </si>
-  <si>
-    <t>J4 Connector - Physical 2x25 Layout</t>
-  </si>
-  <si>
-    <t>Closest connector to the probe-card pin field; carries Devices 17-20. Standard IDC 2xN convention assumed (odd pins = bottom row, even pins = top row, descending left-to-right, Pin 1 at bottom right) - verify against the Pin 1 mark on the physical board before wiring.</t>
-  </si>
-  <si>
-    <t>Top row - pin #</t>
-  </si>
-  <si>
-    <t>Top row - signal</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>Bottom row - pin #</t>
-  </si>
-  <si>
-    <t>Bottom row - signal</t>
-  </si>
-  <si>
-    <t>DAQ ports</t>
-  </si>
-  <si>
-    <t>nc</t>
-  </si>
-  <si>
-    <t>gnd</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>S4</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>Pad</t>
-  </si>
-  <si>
-    <t>Breakout Pin</t>
-  </si>
-  <si>
     <t>Device 01 -&gt; NanoZ DAQ 01, Chip 1. NanoZ package pin 6 not connected.</t>
   </si>
   <si>
@@ -859,91 +1312,16 @@
     <t>This sheet is the probe-needle datasheet only (Accuprobe drawing, "Reference 1" in the wiring manual). It gives the 1-200 land numbering ring and confirms 60+80=140 populated needles, matching "Probe-Card Land #" on the Full Wiring sheet. It does not by itself state which ribbon-connector pin feeds which land number - that correlation comes from the wiring manual's own Appendix B, already merged into the Full Wiring sheet.</t>
   </si>
   <si>
-    <t>S 1</t>
-  </si>
-  <si>
-    <t>S 2</t>
-  </si>
-  <si>
-    <t>S 3</t>
-  </si>
-  <si>
-    <t>S 4</t>
-  </si>
-  <si>
-    <t>D20p6 S 4</t>
-  </si>
-  <si>
-    <t>D20p4 S 3</t>
-  </si>
-  <si>
-    <t>D19p4 S 3</t>
-  </si>
-  <si>
-    <t>D18p4 S 3</t>
-  </si>
-  <si>
-    <t>D17p4 S 3</t>
-  </si>
-  <si>
-    <t>D19p6 S 4</t>
-  </si>
-  <si>
-    <t>D20p3 S 2</t>
-  </si>
-  <si>
-    <t>D20p1 S 1</t>
-  </si>
-  <si>
-    <t>D19p3 S 2</t>
-  </si>
-  <si>
-    <t>D19p1 S 1</t>
-  </si>
-  <si>
-    <t>D18p3 S 2</t>
-  </si>
-  <si>
-    <t>D18p1 S 1</t>
-  </si>
-  <si>
-    <t>D17p3 S 2</t>
-  </si>
-  <si>
-    <t>H 1</t>
-  </si>
-  <si>
-    <t>H 2</t>
-  </si>
-  <si>
-    <t>D19p5 H 2</t>
-  </si>
-  <si>
-    <t>D20p2 H 1</t>
-  </si>
-  <si>
-    <t>D19p2 H 1</t>
-  </si>
-  <si>
-    <t>D18p2 H 1</t>
-  </si>
-  <si>
-    <t>D17p2 H 1</t>
-  </si>
-  <si>
-    <t>D20p5 H 2</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>D20p7 GND</t>
-  </si>
-  <si>
-    <t>Device 20's 7 pins (highlighted): 11 (S 1), 13 (S 2), 14 (H 1), 16 (S 3), 45 (H 2), 47 (GND), 48 (S 4).</t>
-  </si>
-  <si>
-    <t>Die Pads</t>
+    <t xml:space="preserve">Carries Devices 2-10. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carries Devices 1-4. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carries Devices 11-19. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> closest to pins, carries Devices 17-20. </t>
   </si>
 </sst>
 </file>
@@ -998,12 +1376,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF6B7280"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1011,8 +1383,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1034,6 +1412,11 @@
         <fgColor rgb="FFDCFCE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2FE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1047,7 +1430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1066,7 +1449,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1076,7 +1459,23 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1381,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z166"/>
+  <dimension ref="A1:Z197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -1447,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1485,7 +1884,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -1523,7 +1922,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -1561,7 +1960,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -1599,7 +1998,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -1637,7 +2036,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -1675,7 +2074,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>34</v>
@@ -1713,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>36</v>
@@ -1751,7 +2150,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1789,7 +2188,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
@@ -1827,7 +2226,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
@@ -1865,7 +2264,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>42</v>
@@ -1903,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -1941,7 +2340,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>44</v>
@@ -1979,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
@@ -2017,7 +2416,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
@@ -2055,7 +2454,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>49</v>
@@ -2093,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
@@ -2131,7 +2530,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
         <v>51</v>
@@ -2169,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
         <v>52</v>
@@ -2207,7 +2606,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>53</v>
@@ -2245,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -2283,7 +2682,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
         <v>56</v>
@@ -2321,7 +2720,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>57</v>
@@ -2359,7 +2758,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
         <v>58</v>
@@ -2397,7 +2796,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
         <v>59</v>
@@ -2435,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
@@ -2473,7 +2872,7 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>61</v>
@@ -2511,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
         <v>62</v>
@@ -2549,7 +2948,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
         <v>65</v>
@@ -2587,7 +2986,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
         <v>66</v>
@@ -2625,7 +3024,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
         <v>67</v>
@@ -2663,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
         <v>68</v>
@@ -2701,7 +3100,7 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
         <v>69</v>
@@ -2739,7 +3138,7 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>70</v>
@@ -2777,7 +3176,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
         <v>71</v>
@@ -2815,7 +3214,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
         <v>73</v>
@@ -2853,7 +3252,7 @@
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
         <v>74</v>
@@ -2891,7 +3290,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
         <v>75</v>
@@ -2929,7 +3328,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
         <v>76</v>
@@ -2967,7 +3366,7 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
         <v>77</v>
@@ -3005,7 +3404,7 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>78</v>
@@ -3043,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
         <v>79</v>
@@ -3081,7 +3480,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
         <v>82</v>
@@ -3119,7 +3518,7 @@
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
         <v>83</v>
@@ -3157,7 +3556,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
         <v>84</v>
@@ -3195,7 +3594,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
         <v>85</v>
@@ -3233,7 +3632,7 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
         <v>86</v>
@@ -3271,7 +3670,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>87</v>
@@ -3309,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
         <v>88</v>
@@ -3347,7 +3746,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
         <v>90</v>
@@ -3385,7 +3784,7 @@
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
         <v>91</v>
@@ -3423,7 +3822,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
         <v>92</v>
@@ -3461,7 +3860,7 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
         <v>93</v>
@@ -3499,7 +3898,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
         <v>94</v>
@@ -3537,7 +3936,7 @@
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>95</v>
@@ -3575,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
         <v>96</v>
@@ -3613,7 +4012,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
         <v>99</v>
@@ -3651,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
         <v>100</v>
@@ -3689,7 +4088,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D61" t="s">
         <v>101</v>
@@ -3727,7 +4126,7 @@
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D62" t="s">
         <v>102</v>
@@ -3765,7 +4164,7 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
         <v>103</v>
@@ -3803,7 +4202,7 @@
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>104</v>
@@ -3841,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
         <v>105</v>
@@ -3879,7 +4278,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D66" t="s">
         <v>107</v>
@@ -3917,7 +4316,7 @@
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
         <v>108</v>
@@ -3955,7 +4354,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -3993,7 +4392,7 @@
         <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
         <v>110</v>
@@ -4031,7 +4430,7 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D70" t="s">
         <v>111</v>
@@ -4069,7 +4468,7 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>112</v>
@@ -4107,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
         <v>113</v>
@@ -4145,7 +4544,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D73" t="s">
         <v>116</v>
@@ -4183,7 +4582,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
         <v>117</v>
@@ -4221,7 +4620,7 @@
         <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
         <v>118</v>
@@ -4259,7 +4658,7 @@
         <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D76" t="s">
         <v>119</v>
@@ -4297,7 +4696,7 @@
         <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D77" t="s">
         <v>120</v>
@@ -4335,7 +4734,7 @@
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>121</v>
@@ -4373,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
         <v>122</v>
@@ -4411,7 +4810,7 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D80" t="s">
         <v>124</v>
@@ -4449,7 +4848,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
         <v>125</v>
@@ -4487,7 +4886,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D82" t="s">
         <v>126</v>
@@ -4525,7 +4924,7 @@
         <v>5</v>
       </c>
       <c r="C83" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
         <v>127</v>
@@ -4563,7 +4962,7 @@
         <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D84" t="s">
         <v>128</v>
@@ -4601,7 +5000,7 @@
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>129</v>
@@ -4639,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
         <v>130</v>
@@ -4677,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D87" t="s">
         <v>133</v>
@@ -4715,7 +5114,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D88" t="s">
         <v>134</v>
@@ -4753,7 +5152,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D89" t="s">
         <v>135</v>
@@ -4791,7 +5190,7 @@
         <v>5</v>
       </c>
       <c r="C90" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D90" t="s">
         <v>136</v>
@@ -4829,7 +5228,7 @@
         <v>6</v>
       </c>
       <c r="C91" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
         <v>137</v>
@@ -4867,7 +5266,7 @@
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>138</v>
@@ -4905,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D93" t="s">
         <v>139</v>
@@ -4943,7 +5342,7 @@
         <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D94" t="s">
         <v>141</v>
@@ -4981,7 +5380,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
         <v>142</v>
@@ -5019,7 +5418,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D96" t="s">
         <v>143</v>
@@ -5057,7 +5456,7 @@
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
         <v>144</v>
@@ -5095,7 +5494,7 @@
         <v>6</v>
       </c>
       <c r="C98" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D98" t="s">
         <v>145</v>
@@ -5133,7 +5532,7 @@
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>146</v>
@@ -5171,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D100" t="s">
         <v>147</v>
@@ -5209,7 +5608,7 @@
         <v>2</v>
       </c>
       <c r="C101" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D101" t="s">
         <v>150</v>
@@ -5247,7 +5646,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D102" t="s">
         <v>151</v>
@@ -5285,7 +5684,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D103" t="s">
         <v>152</v>
@@ -5323,7 +5722,7 @@
         <v>5</v>
       </c>
       <c r="C104" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D104" t="s">
         <v>153</v>
@@ -5361,7 +5760,7 @@
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D105" t="s">
         <v>154</v>
@@ -5399,7 +5798,7 @@
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>155</v>
@@ -5437,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D107" t="s">
         <v>156</v>
@@ -5475,7 +5874,7 @@
         <v>2</v>
       </c>
       <c r="C108" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D108" t="s">
         <v>158</v>
@@ -5513,7 +5912,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D109" t="s">
         <v>159</v>
@@ -5551,7 +5950,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D110" t="s">
         <v>160</v>
@@ -5589,7 +5988,7 @@
         <v>5</v>
       </c>
       <c r="C111" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D111" t="s">
         <v>161</v>
@@ -5627,7 +6026,7 @@
         <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D112" t="s">
         <v>162</v>
@@ -5665,7 +6064,7 @@
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>163</v>
@@ -5703,7 +6102,7 @@
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D114" t="s">
         <v>164</v>
@@ -5741,7 +6140,7 @@
         <v>2</v>
       </c>
       <c r="C115" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D115" t="s">
         <v>167</v>
@@ -5779,7 +6178,7 @@
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D116" t="s">
         <v>168</v>
@@ -5817,7 +6216,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D117" t="s">
         <v>169</v>
@@ -5855,7 +6254,7 @@
         <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D118" t="s">
         <v>170</v>
@@ -5893,7 +6292,7 @@
         <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D119" t="s">
         <v>171</v>
@@ -5931,7 +6330,7 @@
         <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>172</v>
@@ -5969,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D121" t="s">
         <v>173</v>
@@ -6007,7 +6406,7 @@
         <v>2</v>
       </c>
       <c r="C122" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D122" t="s">
         <v>175</v>
@@ -6045,7 +6444,7 @@
         <v>3</v>
       </c>
       <c r="C123" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
         <v>176</v>
@@ -6083,7 +6482,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D124" t="s">
         <v>177</v>
@@ -6121,7 +6520,7 @@
         <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D125" t="s">
         <v>178</v>
@@ -6159,7 +6558,7 @@
         <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D126" t="s">
         <v>179</v>
@@ -6197,7 +6596,7 @@
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>180</v>
@@ -6235,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="C128" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D128" t="s">
         <v>181</v>
@@ -6273,7 +6672,7 @@
         <v>2</v>
       </c>
       <c r="C129" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D129" t="s">
         <v>184</v>
@@ -6311,7 +6710,7 @@
         <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D130" t="s">
         <v>185</v>
@@ -6349,7 +6748,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -6387,7 +6786,7 @@
         <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D132" t="s">
         <v>187</v>
@@ -6425,7 +6824,7 @@
         <v>6</v>
       </c>
       <c r="C133" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D133" t="s">
         <v>188</v>
@@ -6463,7 +6862,7 @@
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>189</v>
@@ -6501,7 +6900,7 @@
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="D135" t="s">
         <v>190</v>
@@ -6539,7 +6938,7 @@
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="D136" t="s">
         <v>192</v>
@@ -6577,7 +6976,7 @@
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="D137" t="s">
         <v>193</v>
@@ -6615,7 +7014,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D138" t="s">
         <v>194</v>
@@ -6653,7 +7052,7 @@
         <v>5</v>
       </c>
       <c r="C139" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="D139" t="s">
         <v>195</v>
@@ -6691,7 +7090,7 @@
         <v>6</v>
       </c>
       <c r="C140" t="s">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="D140" t="s">
         <v>196</v>
@@ -6729,7 +7128,7 @@
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>197</v>
@@ -6775,454 +7174,1472 @@
       </c>
     </row>
     <row r="148" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="B148" s="15"/>
-      <c r="C148" s="15"/>
-      <c r="D148" s="15"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="15"/>
-      <c r="G148" s="15"/>
-      <c r="H148" s="15"/>
-      <c r="I148" s="15"/>
-      <c r="J148" s="15"/>
-      <c r="K148" s="15"/>
-      <c r="L148" s="15"/>
-      <c r="M148" s="15"/>
-      <c r="N148" s="15"/>
-      <c r="O148" s="15"/>
-      <c r="P148" s="15"/>
-      <c r="Q148" s="15"/>
-      <c r="R148" s="15"/>
-      <c r="S148" s="15"/>
-      <c r="T148" s="15"/>
-      <c r="U148" s="15"/>
-      <c r="V148" s="15"/>
-      <c r="W148" s="15"/>
-      <c r="X148" s="15"/>
-      <c r="Y148" s="15"/>
+      <c r="A148" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="B148" s="23"/>
+      <c r="C148" s="23"/>
+      <c r="D148" s="23"/>
+      <c r="E148" s="23"/>
+      <c r="F148" s="23"/>
+      <c r="G148" s="23"/>
+      <c r="H148" s="23"/>
+      <c r="I148" s="23"/>
+      <c r="J148" s="23"/>
+      <c r="K148" s="23"/>
+      <c r="L148" s="23"/>
+      <c r="M148" s="23"/>
+      <c r="N148" s="23"/>
+      <c r="O148" s="23"/>
+      <c r="P148" s="23"/>
+      <c r="Q148" s="23"/>
+      <c r="R148" s="23"/>
+      <c r="S148" s="23"/>
+      <c r="T148" s="23"/>
+      <c r="U148" s="23"/>
+      <c r="V148" s="23"/>
+      <c r="W148" s="23"/>
+      <c r="X148" s="23"/>
+      <c r="Y148" s="23"/>
     </row>
     <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B150" s="8">
+        <v>201</v>
+      </c>
+      <c r="B150">
         <v>50</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150">
         <v>48</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D150">
         <v>46</v>
       </c>
-      <c r="E150" s="8">
+      <c r="E150">
         <v>44</v>
       </c>
-      <c r="F150" s="8">
+      <c r="F150">
         <v>42</v>
       </c>
-      <c r="G150" s="8">
+      <c r="G150">
         <v>40</v>
       </c>
-      <c r="H150" s="8">
+      <c r="H150">
         <v>38</v>
       </c>
-      <c r="I150" s="8">
+      <c r="I150">
         <v>36</v>
       </c>
-      <c r="J150" s="8">
+      <c r="J150">
         <v>34</v>
       </c>
-      <c r="K150" s="8">
+      <c r="K150">
         <v>32</v>
       </c>
-      <c r="L150" s="8">
+      <c r="L150">
         <v>30</v>
       </c>
-      <c r="M150" s="8">
+      <c r="M150">
         <v>28</v>
       </c>
-      <c r="N150" s="8">
+      <c r="N150">
         <v>26</v>
       </c>
-      <c r="O150" s="8">
+      <c r="O150">
         <v>24</v>
       </c>
-      <c r="P150" s="8">
+      <c r="P150">
         <v>22</v>
       </c>
-      <c r="Q150" s="8">
+      <c r="Q150">
         <v>20</v>
       </c>
-      <c r="R150" s="8">
+      <c r="R150">
         <v>18</v>
       </c>
-      <c r="S150" s="8">
+      <c r="S150">
         <v>16</v>
       </c>
-      <c r="T150" s="8">
+      <c r="T150">
         <v>14</v>
       </c>
-      <c r="U150" s="8">
+      <c r="U150">
         <v>12</v>
       </c>
-      <c r="V150" s="8">
+      <c r="V150">
         <v>10</v>
       </c>
-      <c r="W150" s="8">
+      <c r="W150">
         <v>8</v>
       </c>
-      <c r="X150" s="8">
+      <c r="X150">
         <v>6</v>
       </c>
-      <c r="Y150" s="8">
+      <c r="Y150">
         <v>4</v>
       </c>
-      <c r="Z150" s="8">
+      <c r="Z150">
         <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B151" t="s">
         <v>203</v>
       </c>
-      <c r="B151" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="C151" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D151" s="8" t="s">
+      <c r="C151" t="s">
+        <v>203</v>
+      </c>
+      <c r="D151" t="s">
+        <v>203</v>
+      </c>
+      <c r="E151" t="s">
+        <v>203</v>
+      </c>
+      <c r="F151" t="s">
+        <v>203</v>
+      </c>
+      <c r="G151" t="s">
+        <v>203</v>
+      </c>
+      <c r="H151" t="s">
+        <v>203</v>
+      </c>
+      <c r="I151" t="s">
+        <v>203</v>
+      </c>
+      <c r="J151" t="s">
+        <v>203</v>
+      </c>
+      <c r="K151" t="s">
+        <v>203</v>
+      </c>
+      <c r="L151" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E151" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H151" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="I151" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="J151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="K151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="L151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="M151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="N151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="O151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="P151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="R151" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="S151" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="T151" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="U151" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="V151" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="W151" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="X151" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y151" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z151" s="8" t="s">
-        <v>300</v>
+      <c r="M151" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="N151" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="O151" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="P151" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q151" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="R151" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="S151" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="T151" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="U151" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="V151" t="s">
+        <v>203</v>
+      </c>
+      <c r="W151" t="s">
+        <v>203</v>
+      </c>
+      <c r="X151" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B153" s="8">
+        <v>214</v>
+      </c>
+      <c r="B153">
         <v>49</v>
       </c>
-      <c r="C153" s="8">
+      <c r="C153">
         <v>47</v>
       </c>
-      <c r="D153" s="8">
+      <c r="D153">
         <v>45</v>
       </c>
-      <c r="E153" s="8">
+      <c r="E153">
         <v>43</v>
       </c>
-      <c r="F153" s="8">
+      <c r="F153">
         <v>41</v>
       </c>
-      <c r="G153" s="8">
+      <c r="G153">
         <v>39</v>
       </c>
-      <c r="H153" s="8">
+      <c r="H153">
         <v>37</v>
       </c>
-      <c r="I153" s="8">
+      <c r="I153">
         <v>35</v>
       </c>
-      <c r="J153" s="8">
+      <c r="J153">
         <v>33</v>
       </c>
-      <c r="K153" s="8">
+      <c r="K153">
         <v>31</v>
       </c>
-      <c r="L153" s="8">
+      <c r="L153">
         <v>29</v>
       </c>
-      <c r="M153" s="8">
+      <c r="M153">
         <v>27</v>
       </c>
-      <c r="N153" s="8">
+      <c r="N153">
         <v>25</v>
       </c>
-      <c r="O153" s="8">
+      <c r="O153">
         <v>23</v>
       </c>
-      <c r="P153" s="8">
+      <c r="P153">
         <v>21</v>
       </c>
-      <c r="Q153" s="8">
+      <c r="Q153">
         <v>19</v>
       </c>
-      <c r="R153" s="8">
+      <c r="R153">
         <v>17</v>
       </c>
-      <c r="S153" s="8">
+      <c r="S153">
         <v>15</v>
       </c>
-      <c r="T153" s="8">
+      <c r="T153">
         <v>13</v>
       </c>
-      <c r="U153" s="8">
+      <c r="U153">
         <v>11</v>
       </c>
-      <c r="V153" s="8">
+      <c r="V153">
         <v>9</v>
       </c>
-      <c r="W153" s="8">
+      <c r="W153">
         <v>7</v>
       </c>
-      <c r="X153" s="8">
+      <c r="X153">
         <v>5</v>
       </c>
-      <c r="Y153" s="8">
+      <c r="Y153">
         <v>3</v>
       </c>
-      <c r="Z153" s="8">
+      <c r="Z153">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B154" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B154" t="s">
+        <v>203</v>
+      </c>
+      <c r="C154" t="s">
+        <v>203</v>
+      </c>
+      <c r="D154" t="s">
+        <v>203</v>
+      </c>
+      <c r="E154" t="s">
+        <v>203</v>
+      </c>
+      <c r="F154" t="s">
+        <v>203</v>
+      </c>
+      <c r="G154" t="s">
+        <v>203</v>
+      </c>
+      <c r="H154" t="s">
+        <v>203</v>
+      </c>
+      <c r="I154" t="s">
+        <v>203</v>
+      </c>
+      <c r="J154" t="s">
+        <v>203</v>
+      </c>
+      <c r="K154" t="s">
+        <v>203</v>
+      </c>
+      <c r="L154" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="M154" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="N154" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="O154" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="P154" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q154" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="R154" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="S154" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="T154" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="U154" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="V154" t="s">
+        <v>203</v>
+      </c>
+      <c r="W154" t="s">
+        <v>203</v>
+      </c>
+      <c r="X154" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="157" spans="1:26" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B157" s="23"/>
+      <c r="C157" s="23"/>
+      <c r="D157" s="23"/>
+      <c r="E157" s="23"/>
+      <c r="F157" s="23"/>
+      <c r="G157" s="23"/>
+      <c r="H157" s="23"/>
+      <c r="I157" s="23"/>
+      <c r="J157" s="23"/>
+      <c r="K157" s="23"/>
+      <c r="L157" s="23"/>
+      <c r="M157" s="23"/>
+      <c r="N157" s="23"/>
+      <c r="O157" s="23"/>
+      <c r="P157" s="23"/>
+      <c r="Q157" s="23"/>
+      <c r="R157" s="23"/>
+      <c r="S157" s="23"/>
+      <c r="T157" s="23"/>
+      <c r="U157" s="23"/>
+      <c r="V157" s="23"/>
+      <c r="W157" s="23"/>
+      <c r="X157" s="23"/>
+      <c r="Y157" s="23"/>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A158" s="14" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B160">
+        <v>50</v>
+      </c>
+      <c r="C160">
+        <v>48</v>
+      </c>
+      <c r="D160">
+        <v>46</v>
+      </c>
+      <c r="E160">
+        <v>44</v>
+      </c>
+      <c r="F160">
+        <v>42</v>
+      </c>
+      <c r="G160">
+        <v>40</v>
+      </c>
+      <c r="H160">
+        <v>38</v>
+      </c>
+      <c r="I160">
+        <v>36</v>
+      </c>
+      <c r="J160">
+        <v>34</v>
+      </c>
+      <c r="K160">
+        <v>32</v>
+      </c>
+      <c r="L160">
+        <v>30</v>
+      </c>
+      <c r="M160">
+        <v>28</v>
+      </c>
+      <c r="N160">
+        <v>26</v>
+      </c>
+      <c r="O160">
+        <v>24</v>
+      </c>
+      <c r="P160">
+        <v>22</v>
+      </c>
+      <c r="Q160">
+        <v>20</v>
+      </c>
+      <c r="R160">
+        <v>18</v>
+      </c>
+      <c r="S160">
+        <v>16</v>
+      </c>
+      <c r="T160">
+        <v>14</v>
+      </c>
+      <c r="U160">
+        <v>12</v>
+      </c>
+      <c r="V160">
+        <v>10</v>
+      </c>
+      <c r="W160">
+        <v>8</v>
+      </c>
+      <c r="X160">
+        <v>6</v>
+      </c>
+      <c r="Y160">
+        <v>4</v>
+      </c>
+      <c r="Z160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B161" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D161" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E161" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="G161" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="H161" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I161" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="J161" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K161" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="L161" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="M161" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="N161" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O161" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="P161" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q161" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="R161" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="S161" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="T161" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="U161" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="V161" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="W161" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="X161" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y161" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z161" s="17" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B163">
+        <v>49</v>
+      </c>
+      <c r="C163">
+        <v>47</v>
+      </c>
+      <c r="D163">
+        <v>45</v>
+      </c>
+      <c r="E163">
+        <v>43</v>
+      </c>
+      <c r="F163">
+        <v>41</v>
+      </c>
+      <c r="G163">
+        <v>39</v>
+      </c>
+      <c r="H163">
+        <v>37</v>
+      </c>
+      <c r="I163">
+        <v>35</v>
+      </c>
+      <c r="J163">
+        <v>33</v>
+      </c>
+      <c r="K163">
+        <v>31</v>
+      </c>
+      <c r="L163">
+        <v>29</v>
+      </c>
+      <c r="M163">
+        <v>27</v>
+      </c>
+      <c r="N163">
+        <v>25</v>
+      </c>
+      <c r="O163">
+        <v>23</v>
+      </c>
+      <c r="P163">
+        <v>21</v>
+      </c>
+      <c r="Q163">
+        <v>19</v>
+      </c>
+      <c r="R163">
+        <v>17</v>
+      </c>
+      <c r="S163">
+        <v>15</v>
+      </c>
+      <c r="T163">
+        <v>13</v>
+      </c>
+      <c r="U163">
+        <v>11</v>
+      </c>
+      <c r="V163">
+        <v>9</v>
+      </c>
+      <c r="W163">
+        <v>7</v>
+      </c>
+      <c r="X163">
+        <v>5</v>
+      </c>
+      <c r="Y163">
+        <v>3</v>
+      </c>
+      <c r="Z163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="D164" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="E164" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="F164" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="G164" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="H164" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I164" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="J164" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="K164" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="L164" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="M164" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="N164" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="O164" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="P164" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q164" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="R164" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="S164" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="T164" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="U164" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="V164" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="W164" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="X164" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y164" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z164" s="16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="167" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A168" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A170" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B170">
+        <v>50</v>
+      </c>
+      <c r="C170">
+        <v>48</v>
+      </c>
+      <c r="D170">
+        <v>46</v>
+      </c>
+      <c r="E170">
+        <v>44</v>
+      </c>
+      <c r="F170">
+        <v>42</v>
+      </c>
+      <c r="G170">
+        <v>40</v>
+      </c>
+      <c r="H170">
+        <v>38</v>
+      </c>
+      <c r="I170">
+        <v>36</v>
+      </c>
+      <c r="J170">
+        <v>34</v>
+      </c>
+      <c r="K170">
+        <v>32</v>
+      </c>
+      <c r="L170">
+        <v>30</v>
+      </c>
+      <c r="M170">
+        <v>28</v>
+      </c>
+      <c r="N170">
+        <v>26</v>
+      </c>
+      <c r="O170">
+        <v>24</v>
+      </c>
+      <c r="P170">
+        <v>22</v>
+      </c>
+      <c r="Q170">
+        <v>20</v>
+      </c>
+      <c r="R170">
+        <v>18</v>
+      </c>
+      <c r="S170">
+        <v>16</v>
+      </c>
+      <c r="T170">
+        <v>14</v>
+      </c>
+      <c r="U170">
+        <v>12</v>
+      </c>
+      <c r="V170">
+        <v>10</v>
+      </c>
+      <c r="W170">
+        <v>8</v>
+      </c>
+      <c r="X170">
+        <v>6</v>
+      </c>
+      <c r="Y170">
+        <v>4</v>
+      </c>
+      <c r="Z170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B171" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="D171" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E171" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="F171" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="G171" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="H171" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="I171" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="J171" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="K171" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="L171" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="M171" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="N171" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="O171" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="P171" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q171" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="R171" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="S171" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="T171" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="U171" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="V171" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="W171" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="X171" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y171" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z171" s="16" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B173">
+        <v>49</v>
+      </c>
+      <c r="C173">
+        <v>47</v>
+      </c>
+      <c r="D173">
+        <v>45</v>
+      </c>
+      <c r="E173">
+        <v>43</v>
+      </c>
+      <c r="F173">
+        <v>41</v>
+      </c>
+      <c r="G173">
+        <v>39</v>
+      </c>
+      <c r="H173">
+        <v>37</v>
+      </c>
+      <c r="I173">
+        <v>35</v>
+      </c>
+      <c r="J173">
+        <v>33</v>
+      </c>
+      <c r="K173">
+        <v>31</v>
+      </c>
+      <c r="L173">
+        <v>29</v>
+      </c>
+      <c r="M173">
+        <v>27</v>
+      </c>
+      <c r="N173">
+        <v>25</v>
+      </c>
+      <c r="O173">
+        <v>23</v>
+      </c>
+      <c r="P173">
+        <v>21</v>
+      </c>
+      <c r="Q173">
+        <v>19</v>
+      </c>
+      <c r="R173">
+        <v>17</v>
+      </c>
+      <c r="S173">
+        <v>15</v>
+      </c>
+      <c r="T173">
+        <v>13</v>
+      </c>
+      <c r="U173">
+        <v>11</v>
+      </c>
+      <c r="V173">
+        <v>9</v>
+      </c>
+      <c r="W173">
+        <v>7</v>
+      </c>
+      <c r="X173">
+        <v>5</v>
+      </c>
+      <c r="Y173">
+        <v>3</v>
+      </c>
+      <c r="Z173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B174" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="D154" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G154" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H154" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="I154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="J154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="K154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="L154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="M154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="N154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="O154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="P154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="R154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="S154" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="T154" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="U154" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="V154" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="W154" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="X154" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="Y154" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="Z154" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A156" s="14" t="s">
+      <c r="C174" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="B156" s="15"/>
-      <c r="C156" s="15"/>
-      <c r="D156" s="15"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="15"/>
-      <c r="G156" s="15"/>
-      <c r="H156" s="15"/>
-      <c r="I156" s="15"/>
-      <c r="J156" s="15"/>
-      <c r="K156" s="15"/>
-      <c r="L156" s="15"/>
-      <c r="M156" s="15"/>
-      <c r="N156" s="15"/>
-      <c r="O156" s="15"/>
-      <c r="P156" s="15"/>
-      <c r="Q156" s="15"/>
-      <c r="R156" s="15"/>
-      <c r="S156" s="15"/>
-      <c r="T156" s="15"/>
-      <c r="U156" s="15"/>
-      <c r="V156" s="15"/>
-      <c r="W156" s="15"/>
-      <c r="X156" s="15"/>
-      <c r="Y156" s="15"/>
-    </row>
-    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A159" s="10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>208</v>
-      </c>
-      <c r="B160" t="s">
-        <v>209</v>
-      </c>
-      <c r="C160" t="s">
-        <v>210</v>
-      </c>
-      <c r="D160" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>212</v>
-      </c>
-      <c r="B161" t="s">
-        <v>213</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="D174" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E174" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="F174" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="G174" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="H174" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="I174" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="J174" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K174" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="L174" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="M174" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="N174" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="O174" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="P174" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q174" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="R174" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="S174" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="T174" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="U174" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="V174" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="W174" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="X174" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="Y174" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z174" s="16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="177" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A178" s="14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B180" s="8">
+        <v>50</v>
+      </c>
+      <c r="C180" s="8">
+        <v>48</v>
+      </c>
+      <c r="D180" s="8">
+        <v>46</v>
+      </c>
+      <c r="E180" s="8">
+        <v>44</v>
+      </c>
+      <c r="F180" s="8">
+        <v>42</v>
+      </c>
+      <c r="G180" s="8">
+        <v>40</v>
+      </c>
+      <c r="H180" s="8">
+        <v>38</v>
+      </c>
+      <c r="I180" s="8">
+        <v>36</v>
+      </c>
+      <c r="J180" s="8">
+        <v>34</v>
+      </c>
+      <c r="K180" s="8">
+        <v>32</v>
+      </c>
+      <c r="L180" s="8">
+        <v>30</v>
+      </c>
+      <c r="M180" s="8">
+        <v>28</v>
+      </c>
+      <c r="N180" s="8">
+        <v>26</v>
+      </c>
+      <c r="O180" s="8">
+        <v>24</v>
+      </c>
+      <c r="P180" s="8">
+        <v>22</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>20</v>
+      </c>
+      <c r="R180" s="8">
+        <v>18</v>
+      </c>
+      <c r="S180" s="8">
+        <v>16</v>
+      </c>
+      <c r="T180" s="8">
+        <v>14</v>
+      </c>
+      <c r="U180" s="8">
+        <v>12</v>
+      </c>
+      <c r="V180" s="8">
+        <v>10</v>
+      </c>
+      <c r="W180" s="8">
+        <v>8</v>
+      </c>
+      <c r="X180" s="8">
+        <v>6</v>
+      </c>
+      <c r="Y180" s="8">
+        <v>4</v>
+      </c>
+      <c r="Z180" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="C181" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="J181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="L181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="N181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="O181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="P181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="R181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="S181" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="T181" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="U181" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="V181" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="W181" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="X181" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y181" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z181" s="18" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D161" t="s">
+      <c r="B183" s="8">
+        <v>49</v>
+      </c>
+      <c r="C183" s="8">
+        <v>47</v>
+      </c>
+      <c r="D183" s="8">
+        <v>45</v>
+      </c>
+      <c r="E183" s="8">
+        <v>43</v>
+      </c>
+      <c r="F183" s="8">
+        <v>41</v>
+      </c>
+      <c r="G183" s="8">
+        <v>39</v>
+      </c>
+      <c r="H183" s="8">
+        <v>37</v>
+      </c>
+      <c r="I183" s="8">
+        <v>35</v>
+      </c>
+      <c r="J183" s="8">
+        <v>33</v>
+      </c>
+      <c r="K183" s="8">
+        <v>31</v>
+      </c>
+      <c r="L183" s="8">
+        <v>29</v>
+      </c>
+      <c r="M183" s="8">
+        <v>27</v>
+      </c>
+      <c r="N183" s="8">
+        <v>25</v>
+      </c>
+      <c r="O183" s="8">
+        <v>23</v>
+      </c>
+      <c r="P183" s="8">
+        <v>21</v>
+      </c>
+      <c r="Q183" s="8">
+        <v>19</v>
+      </c>
+      <c r="R183" s="8">
+        <v>17</v>
+      </c>
+      <c r="S183" s="8">
+        <v>15</v>
+      </c>
+      <c r="T183" s="8">
+        <v>13</v>
+      </c>
+      <c r="U183" s="8">
+        <v>11</v>
+      </c>
+      <c r="V183" s="8">
+        <v>9</v>
+      </c>
+      <c r="W183" s="8">
+        <v>7</v>
+      </c>
+      <c r="X183" s="8">
+        <v>5</v>
+      </c>
+      <c r="Y183" s="8">
+        <v>3</v>
+      </c>
+      <c r="Z183" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A184" s="7" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="10" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>214</v>
-      </c>
-      <c r="B163" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>215</v>
-      </c>
-      <c r="B164" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>211</v>
-      </c>
-      <c r="B165" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>210</v>
+      <c r="B184" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="C184" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G184" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="H184" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="J184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="L184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="N184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="O184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="P184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="R184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="S184" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="T184" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="U184" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="V184" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="W184" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="X184" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y184" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z184" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="187" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A187" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>350</v>
+      </c>
+      <c r="B188" t="s">
+        <v>358</v>
+      </c>
+      <c r="C188" t="s">
+        <v>357</v>
+      </c>
+      <c r="D188" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>355</v>
+      </c>
+      <c r="B189" t="s">
+        <v>354</v>
+      </c>
+      <c r="C189" t="s">
+        <v>351</v>
+      </c>
+      <c r="D189" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A190" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>352</v>
+      </c>
+      <c r="B191" t="s">
+        <v>351</v>
+      </c>
+      <c r="C191" t="s">
+        <v>354</v>
+      </c>
+      <c r="D191" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>356</v>
+      </c>
+      <c r="B192" t="s">
+        <v>357</v>
+      </c>
+      <c r="C192" t="s">
+        <v>358</v>
+      </c>
+      <c r="D192" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>358</v>
+      </c>
+      <c r="B194" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>350</v>
+      </c>
+      <c r="B195" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>355</v>
+      </c>
+      <c r="B196" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L141" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
-    <mergeCell ref="A156:Y156"/>
+    <mergeCell ref="A157:Y157"/>
     <mergeCell ref="A148:Y148"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7245,7 +8662,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -7257,7 +8674,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>217</v>
+        <v>361</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -7268,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>362</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -7288,7 +8705,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -7308,7 +8725,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -7328,7 +8745,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>365</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
@@ -7348,7 +8765,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
@@ -7368,7 +8785,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>367</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -7388,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>368</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -7405,7 +8822,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>218</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -7426,16 +8843,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>370</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>372</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7443,13 +8860,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>375</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7457,13 +8874,13 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s">
-        <v>226</v>
+        <v>377</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7471,13 +8888,13 @@
         <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>378</v>
       </c>
       <c r="D4" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7485,13 +8902,13 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7499,13 +8916,13 @@
         <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="D6" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -7513,13 +8930,13 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C7" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="D7" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -7527,13 +8944,13 @@
         <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -7541,13 +8958,13 @@
         <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C9" t="s">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -7555,13 +8972,13 @@
         <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -7569,83 +8986,83 @@
         <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="C11" t="s">
-        <v>234</v>
+        <v>385</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>235</v>
+        <v>386</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="C12" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D12" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>389</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>390</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="C14" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D14" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>391</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="C15" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D15" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>241</v>
+        <v>392</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D16" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -7664,148 +9081,148 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>242</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>243</v>
+        <v>394</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>396</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>398</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>404</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>406</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>257</v>
+        <v>408</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>259</v>
+        <v>410</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>261</v>
+        <v>412</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>263</v>
+        <v>414</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>416</v>
       </c>
       <c r="B14" t="s">
-        <v>266</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>418</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>420</v>
       </c>
       <c r="B16" t="s">
-        <v>270</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>271</v>
+        <v>422</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>273</v>
+        <v>424</v>
       </c>
       <c r="B18" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>276</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
